--- a/anton_new_import_test_data.xlsx
+++ b/anton_new_import_test_data.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10509"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ak/Dropbox/anton_import_test_data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81FCEAA-40B4-0A4F-8835-80DE9581B8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="27900" windowHeight="17380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="import_tabelle" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="import_tabelle" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -20,273 +25,273 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="255">
-  <si>
-    <t xml:space="preserve">parent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">signatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">identifier_old</t>
-  </si>
-  <si>
-    <t xml:space="preserve">title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_date_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_date_start_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_date_end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_date_end_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_event_details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_place</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_place_address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date_comment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level_of_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">object_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">object_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extent_lfm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creation_actors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sprachen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vacat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">private_media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">poster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digitisation_actors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digitisation_date_start_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digitisation_date_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">digitisation_date_end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keywords_terms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keywords_places</t>
-  </si>
-  <si>
-    <t xml:space="preserve">keywords_actors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">period_of_protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status_of_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">detail_of_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">extent_text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bioghist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">custod_hist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scopecontent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">appraisal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">accruals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arrangement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">condition_of_access</t>
-  </si>
-  <si>
-    <t xml:space="preserve">condition_of_reproduction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">language_script</t>
-  </si>
-  <si>
-    <t xml:space="preserve">physical_description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">finding_aids</t>
-  </si>
-  <si>
-    <t xml:space="preserve">location_details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reproductions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">related_units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">general_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">internal_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archivists_notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rules_note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">provenance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loan_users</t>
-  </si>
-  <si>
-    <t xml:space="preserve">loan_date_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_date_start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_date_start_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_date_end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_date_end_ca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_actors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acquisition_event_details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRA 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flyer für Anton (Version 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015-10-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiedikon / Zürich (ZH)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waserstrasse 61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datum des letzten Ausdrucks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Einzelstück</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle &amp; Ritter (2004-2020)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deutsch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spritzenhaus Waser 585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anton_flyer.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Werbung, Anton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zürich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Din A4, doppelseitig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Flyer für die Archivdatenbank Anton. Enthält grobe Funktionsbeschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton das Erdferkel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007-07-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archives of Scott Foresman and Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logo.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton, Logo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 digitales Bild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vorlage für Logo</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="257">
+  <si>
+    <t>parent</t>
+  </si>
+  <si>
+    <t>signatur</t>
+  </si>
+  <si>
+    <t>identifier_old</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>creation_date_start</t>
+  </si>
+  <si>
+    <t>creation_date_start_ca</t>
+  </si>
+  <si>
+    <t>creation_date_end</t>
+  </si>
+  <si>
+    <t>creation_date_end_ca</t>
+  </si>
+  <si>
+    <t>creation_event_details</t>
+  </si>
+  <si>
+    <t>creation_place</t>
+  </si>
+  <si>
+    <t>creation_place_address</t>
+  </si>
+  <si>
+    <t>date_comment</t>
+  </si>
+  <si>
+    <t>level_of_description</t>
+  </si>
+  <si>
+    <t>object_type</t>
+  </si>
+  <si>
+    <t>object_count</t>
+  </si>
+  <si>
+    <t>extent_lfm</t>
+  </si>
+  <si>
+    <t>creation_actors</t>
+  </si>
+  <si>
+    <t>sprachen</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>vacat</t>
+  </si>
+  <si>
+    <t>private_media</t>
+  </si>
+  <si>
+    <t>media</t>
+  </si>
+  <si>
+    <t>poster</t>
+  </si>
+  <si>
+    <t>digitisation_actors</t>
+  </si>
+  <si>
+    <t>digitisation_date_start_ca</t>
+  </si>
+  <si>
+    <t>digitisation_date_start</t>
+  </si>
+  <si>
+    <t>digitisation_date_end</t>
+  </si>
+  <si>
+    <t>keywords_terms</t>
+  </si>
+  <si>
+    <t>keywords_places</t>
+  </si>
+  <si>
+    <t>keywords_actors</t>
+  </si>
+  <si>
+    <t>period_of_protection</t>
+  </si>
+  <si>
+    <t>status_of_description</t>
+  </si>
+  <si>
+    <t>detail_of_description</t>
+  </si>
+  <si>
+    <t>private</t>
+  </si>
+  <si>
+    <t>extent_text</t>
+  </si>
+  <si>
+    <t>bioghist</t>
+  </si>
+  <si>
+    <t>custod_hist</t>
+  </si>
+  <si>
+    <t>scopecontent</t>
+  </si>
+  <si>
+    <t>appraisal</t>
+  </si>
+  <si>
+    <t>accruals</t>
+  </si>
+  <si>
+    <t>arrangement</t>
+  </si>
+  <si>
+    <t>condition_of_access</t>
+  </si>
+  <si>
+    <t>condition_of_reproduction</t>
+  </si>
+  <si>
+    <t>language_script</t>
+  </si>
+  <si>
+    <t>physical_description</t>
+  </si>
+  <si>
+    <t>finding_aids</t>
+  </si>
+  <si>
+    <t>location_details</t>
+  </si>
+  <si>
+    <t>reproductions</t>
+  </si>
+  <si>
+    <t>related_units</t>
+  </si>
+  <si>
+    <t>publications</t>
+  </si>
+  <si>
+    <t>general_note</t>
+  </si>
+  <si>
+    <t>internal_note</t>
+  </si>
+  <si>
+    <t>archivists_notes</t>
+  </si>
+  <si>
+    <t>rules_note</t>
+  </si>
+  <si>
+    <t>provenance</t>
+  </si>
+  <si>
+    <t>loan_users</t>
+  </si>
+  <si>
+    <t>loan_date_start</t>
+  </si>
+  <si>
+    <t>acquisition_date_start</t>
+  </si>
+  <si>
+    <t>acquisition_date_start_ca</t>
+  </si>
+  <si>
+    <t>acquisition_date_end</t>
+  </si>
+  <si>
+    <t>acquisition_date_end_ca</t>
+  </si>
+  <si>
+    <t>acquisition_actors</t>
+  </si>
+  <si>
+    <t>acquisition_event_details</t>
+  </si>
+  <si>
+    <t>KRA 1</t>
+  </si>
+  <si>
+    <t>Flyer für Anton (Version 1)</t>
+  </si>
+  <si>
+    <t>2015-10-29</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Wiedikon / Zürich (ZH)</t>
+  </si>
+  <si>
+    <t>Waserstrasse 61</t>
+  </si>
+  <si>
+    <t>Datum des letzten Ausdrucks</t>
+  </si>
+  <si>
+    <t>Einzelstück</t>
+  </si>
+  <si>
+    <t>Akte</t>
+  </si>
+  <si>
+    <t>Kränzle &amp; Ritter (2004-2020)</t>
+  </si>
+  <si>
+    <t>Deutsch</t>
+  </si>
+  <si>
+    <t>Spritzenhaus Waser 585</t>
+  </si>
+  <si>
+    <t>anton_flyer.pdf</t>
+  </si>
+  <si>
+    <t>Werbung, Anton</t>
+  </si>
+  <si>
+    <t>Zürich</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>Din A4, doppelseitig</t>
+  </si>
+  <si>
+    <t>Flyer für die Archivdatenbank Anton. Enthält grobe Funktionsbeschreibung</t>
+  </si>
+  <si>
+    <t>Anton das Erdferkel</t>
+  </si>
+  <si>
+    <t>2007-07-25</t>
+  </si>
+  <si>
+    <t>Bild</t>
+  </si>
+  <si>
+    <t>Archives of Scott Foresman and Company</t>
+  </si>
+  <si>
+    <t>logo.png</t>
+  </si>
+  <si>
+    <t>Anton, Logo</t>
+  </si>
+  <si>
+    <t>1 digitales Bild</t>
+  </si>
+  <si>
+    <t>Vorlage für Logo</t>
   </si>
   <si>
     <r>
@@ -294,21 +299,20 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <family val="0"/>
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">This work has been released into the </t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">public domain</t>
+      <t>public domain</t>
     </r>
     <r>
       <rPr>
@@ -322,14 +326,14 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
+        <b/>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Pearson Scott Foresman</t>
+      <t>Pearson Scott Foresman</t>
     </r>
     <r>
       <rPr>
@@ -339,535 +343,521 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. This applies worldwide. (vgl. &lt;a href="https://commons.wikimedia.org/wiki/File:Aardvark2_(PSF).png"&gt;wikimedia&lt;/a&gt;)</t>
+      <t>. This applies worldwide. (vgl. &lt;a href="https://commons.wikimedia.org/wiki/File:Aardvark2_(PSF).png"&gt;wikimedia&lt;/a&gt;)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Datenimport in Anton (Video)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016-11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Film</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle &amp; Ritter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">import-data.mov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemuphones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton, Tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Video (1 Min. 8 Sec)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kein Ton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRA 1/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRA 5</t>
+    <t>Datenimport in Anton (Video)</t>
+  </si>
+  <si>
+    <t>2016-11-01</t>
+  </si>
+  <si>
+    <t>Film</t>
+  </si>
+  <si>
+    <t>Kränzle &amp; Ritter</t>
+  </si>
+  <si>
+    <t>import-data.mov</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Lemuphones</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>Anton, Tutorial</t>
+  </si>
+  <si>
+    <t>1 Video (1 Min. 8 Sec)</t>
+  </si>
+  <si>
+    <t>kein Ton</t>
+  </si>
+  <si>
+    <t>KRA 1/1</t>
+  </si>
+  <si>
+    <t>KRA 5</t>
   </si>
   <si>
     <t xml:space="preserve">Andreas Kränzle, Andreas Meyerhans, Bettina Mosca-Rau (Hgg.): Von guten Taten und Bullen. Geschichten aus Archiv und Musikbibliothek des Klosters Einsiedeln, Einsiedeln 2012. </t>
   </si>
   <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dossier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band</t>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>Dossier</t>
+  </si>
+  <si>
+    <t>Band</t>
   </si>
   <si>
     <t xml:space="preserve">Kränzle, Andreas; Meyerhans, Andreas; Mosca-Rau, Bettina </t>
   </si>
   <si>
-    <t xml:space="preserve">Einsiedeln_Archivf_cover.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kloster Einsiedeln, Publikation, Archiv Reorganisation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle, Andreas; Meyerhans, Andreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">216 Seiten; ca. DinA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enthält als Einleitung Abschlussbericht zur Reorganisation des Klosterarchivs (2005-2012)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Die 4 Klosterorganisten in Concert. Kompositionen aus der Musikbibliothek Einsiedeln</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helg, Pater Lukas; Koch, Pater Ambros; Flury, Pater Theo; Höfliger, Pater Basil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">in_concert.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kloster Einsiedeln, Musik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helg, Pater Lukas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRA 7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nationalhymne von Santa Lemusa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012-11-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemuphones (2005-2018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Französisch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lemuphones_Nationalhymne_von_Santa_Lemusa.mp3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Musik, Brass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Es kursieren auf Santa Lemusa verschiedene Nationalhymnen – unter anderem eine sehr süffige Melodie des Komponisten Féréol Ricochet. Am 1. August 2012 aber erklärte Staatspräsident Samson Godet die hier vorgestellte Musik zur offiziellen Landeshymne und forderte die Bewohner der Insel in einer ergreifenden Rede auf, den Text bald auswendig zu lernen.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je ne regrette rien</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugener, Rainer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Je_ne_regrette_rien2.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arrangement für 2 Tr, 1 Euph, 1 Pos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Man of La Mancha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Man_of_La_Mancha.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr. Sandmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mr_Sandman.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRA 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L'Archiviste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Érik Desmazières</t>
-  </si>
-  <si>
-    <t xml:space="preserve">archivistebg.jpg::archivistebg.tif</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kunst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prolonged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blattgrösse: ca. 26.5 x 20 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radierung, Aquatinta und Roulette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altsignatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vollständiger Testdatensatz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Details zur Erstellung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Augsburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kommentar zur Datierung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deutsch::Englisch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gubler AG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anton, Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witikon / Zürich (ZH)::Bern (BE)::Aargau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle &amp; Ritter;Meyerhans, Andreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">full</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Umfang Beschreibung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verwaltungsgeschichte/Biografie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bestandsgeschichte</t>
+    <t>Einsiedeln_Archivf_cover.jpg</t>
+  </si>
+  <si>
+    <t>Kloster Einsiedeln, Publikation, Archiv Reorganisation</t>
+  </si>
+  <si>
+    <t>Kränzle, Andreas; Meyerhans, Andreas</t>
+  </si>
+  <si>
+    <t>216 Seiten; ca. DinA4</t>
+  </si>
+  <si>
+    <t>Enthält als Einleitung Abschlussbericht zur Reorganisation des Klosterarchivs (2005-2012)</t>
+  </si>
+  <si>
+    <t>Die 4 Klosterorganisten in Concert. Kompositionen aus der Musikbibliothek Einsiedeln</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>Helg, Pater Lukas; Koch, Pater Ambros; Flury, Pater Theo; Höfliger, Pater Basil</t>
+  </si>
+  <si>
+    <t>in_concert.jpg</t>
+  </si>
+  <si>
+    <t>Kloster Einsiedeln, Musik</t>
+  </si>
+  <si>
+    <t>Helg, Pater Lukas</t>
+  </si>
+  <si>
+    <t>KRA 7</t>
+  </si>
+  <si>
+    <t>Nationalhymne von Santa Lemusa</t>
+  </si>
+  <si>
+    <t>2012-11-12</t>
+  </si>
+  <si>
+    <t>Ton</t>
+  </si>
+  <si>
+    <t>Lemuphones (2005-2018)</t>
+  </si>
+  <si>
+    <t>Französisch</t>
+  </si>
+  <si>
+    <t>Lemuphones_Nationalhymne_von_Santa_Lemusa.mp3</t>
+  </si>
+  <si>
+    <t>Musik, Brass</t>
+  </si>
+  <si>
+    <t>Es kursieren auf Santa Lemusa verschiedene Nationalhymnen – unter anderem eine sehr süffige Melodie des Komponisten Féréol Ricochet. Am 1. August 2012 aber erklärte Staatspräsident Samson Godet die hier vorgestellte Musik zur offiziellen Landeshymne und forderte die Bewohner der Insel in einer ergreifenden Rede auf, den Text bald auswendig zu lernen.</t>
+  </si>
+  <si>
+    <t>Je ne regrette rien</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Hugener, Rainer</t>
+  </si>
+  <si>
+    <t>Je_ne_regrette_rien2.pdf</t>
+  </si>
+  <si>
+    <t>standard</t>
+  </si>
+  <si>
+    <t>Arrangement für 2 Tr, 1 Euph, 1 Pos</t>
+  </si>
+  <si>
+    <t>Man of La Mancha</t>
+  </si>
+  <si>
+    <t>Man_of_La_Mancha.pdf</t>
+  </si>
+  <si>
+    <t>Mr. Sandmann</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>Mr_Sandman.pdf</t>
+  </si>
+  <si>
+    <t>KRA 9</t>
+  </si>
+  <si>
+    <t>L'Archiviste</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>Érik Desmazières</t>
+  </si>
+  <si>
+    <t>archivistebg.jpg::archivistebg.tif</t>
+  </si>
+  <si>
+    <t>Kunst</t>
+  </si>
+  <si>
+    <t>prolonged</t>
+  </si>
+  <si>
+    <t>Blattgrösse: ca. 26.5 x 20 cm</t>
+  </si>
+  <si>
+    <t>Radierung, Aquatinta und Roulette</t>
+  </si>
+  <si>
+    <t>Test 1</t>
+  </si>
+  <si>
+    <t>Altsignatur</t>
+  </si>
+  <si>
+    <t>Vollständiger Testdatensatz</t>
+  </si>
+  <si>
+    <t>2000-01-01</t>
+  </si>
+  <si>
+    <t>2000-12-31</t>
+  </si>
+  <si>
+    <t>Details zur Erstellung</t>
+  </si>
+  <si>
+    <t>Augsburg</t>
+  </si>
+  <si>
+    <t>Kommentar zur Datierung</t>
+  </si>
+  <si>
+    <t>Deutsch::Englisch</t>
+  </si>
+  <si>
+    <t>Gubler AG</t>
+  </si>
+  <si>
+    <t>Anton, Test</t>
+  </si>
+  <si>
+    <t>Witikon / Zürich (ZH)::Bern (BE)::Aargau</t>
+  </si>
+  <si>
+    <t>Kränzle &amp; Ritter;Meyerhans, Andreas</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>full</t>
+  </si>
+  <si>
+    <t>Umfang Beschreibung</t>
+  </si>
+  <si>
+    <t>Verwaltungsgeschichte/Biografie</t>
+  </si>
+  <si>
+    <t>Bestandsgeschichte</t>
   </si>
   <si>
     <t xml:space="preserve">Form und Inhalt. Es wurden sämtliche Felder beim automatischen Import ausgefüllt. </t>
   </si>
   <si>
-    <t xml:space="preserve">Bewertung und Kassation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuzugänge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ordnung und Klassifikation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zugangsbedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reproduktionsbedingungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sprache, Schrift (note)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Physische Beschaffenheit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Findhilfsmittel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standort der Originale (Note)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kopien und Reproduktionen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verwandte Verzeichnungseinheiten: Test 2/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publikationen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allgemeine Anmerkungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Archivinterne Anmerkungen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information des Bearbeiters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Verzeichnungsgrundsätze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit Standard Sperrfrist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_sperrfrist.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit verlängerter Sperrfrist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verlängerte_sperrfrist.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit Film</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2001-03-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Minute</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">private.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">manuelle Signatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit manueller Signatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit abgelaufener Standard Sperrfrist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1970</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Griechisch, alt (bis 1453)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_sperrfrist_abgelaufen.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz mit abgelaufener verlängerter Schutzfrist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">verlaengerte_sperrfrist_abgelaufen.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz ausgeliehen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anton, admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1911-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Recordgroup (für Tektonik-Tests)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bestandsgruppe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sammlung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 3 Bestand (über Excel importiert)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bestand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1913-01-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle, Andreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hier kommt der Kommentar zur Acquisition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dossier aus München</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">München</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grissemann &amp; Stermann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dossier aus Zürich und Ausgburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zürich und Augsburg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz Vacat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aus Excel erzeugte Hierachie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Datensatz in Test gelöscht</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz gesperrt und PDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gesperrtes_pdf.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz privat mit PDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">privates_pdf.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testdatensatz Akteur am Namen erkennen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Ortsname Stadt als Stadt erkennen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aargau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Name als Name erkennen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Witikon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kränzle, Andreas (Historiker)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesperrtes Bild</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gesperrtes_Bild.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 3</t>
+    <t>Bewertung und Kassation</t>
+  </si>
+  <si>
+    <t>Neuzugänge</t>
+  </si>
+  <si>
+    <t>Ordnung und Klassifikation</t>
+  </si>
+  <si>
+    <t>Zugangsbedingungen</t>
+  </si>
+  <si>
+    <t>Reproduktionsbedingungen</t>
+  </si>
+  <si>
+    <t>Sprache, Schrift (note)</t>
+  </si>
+  <si>
+    <t>Physische Beschaffenheit</t>
+  </si>
+  <si>
+    <t>Findhilfsmittel</t>
+  </si>
+  <si>
+    <t>Standort der Originale (Note)</t>
+  </si>
+  <si>
+    <t>Kopien und Reproduktionen</t>
+  </si>
+  <si>
+    <t>Verwandte Verzeichnungseinheiten: Test 2/1</t>
+  </si>
+  <si>
+    <t>Publikationen</t>
+  </si>
+  <si>
+    <t>Allgemeine Anmerkungen</t>
+  </si>
+  <si>
+    <t>Archivinterne Anmerkungen</t>
+  </si>
+  <si>
+    <t>Information des Bearbeiters</t>
+  </si>
+  <si>
+    <t>Verzeichnungsgrundsätze</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit Standard Sperrfrist</t>
+  </si>
+  <si>
+    <t>standard_sperrfrist.png</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit verlängerter Sperrfrist</t>
+  </si>
+  <si>
+    <t>verlängerte_sperrfrist.png</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit Film</t>
+  </si>
+  <si>
+    <t>2001-03-02</t>
+  </si>
+  <si>
+    <t>1 Minute</t>
+  </si>
+  <si>
+    <t>Testdatensatz private</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>private.png</t>
+  </si>
+  <si>
+    <t>manuelle Signatur</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit manueller Signatur</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit abgelaufener Standard Sperrfrist</t>
+  </si>
+  <si>
+    <t>1970</t>
+  </si>
+  <si>
+    <t>Griechisch, alt (bis 1453)</t>
+  </si>
+  <si>
+    <t>standard_sperrfrist_abgelaufen.png</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit abgelaufener verlängerter Schutzfrist</t>
+  </si>
+  <si>
+    <t>1900</t>
+  </si>
+  <si>
+    <t>verlaengerte_sperrfrist_abgelaufen.png</t>
+  </si>
+  <si>
+    <t>Testdatensatz ausgeliehen</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>anton, admin</t>
+  </si>
+  <si>
+    <t>1911-01-01</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Test Recordgroup (für Tektonik-Tests)</t>
+  </si>
+  <si>
+    <t>Bestandsgruppe</t>
+  </si>
+  <si>
+    <t>Sammlung</t>
+  </si>
+  <si>
+    <t>Test 3 Bestand (über Excel importiert)</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>Bestand</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>final</t>
+  </si>
+  <si>
+    <t>1913-01-03</t>
+  </si>
+  <si>
+    <t>1917</t>
+  </si>
+  <si>
+    <t>Kränzle, Andreas</t>
+  </si>
+  <si>
+    <t>Hier kommt der Kommentar zur Acquisition</t>
+  </si>
+  <si>
+    <t>Test 2</t>
+  </si>
+  <si>
+    <t>Test 2/1</t>
+  </si>
+  <si>
+    <t>Dossier aus München</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>München</t>
+  </si>
+  <si>
+    <t>Grissemann &amp; Stermann</t>
+  </si>
+  <si>
+    <t>Test 2/2</t>
+  </si>
+  <si>
+    <t>Dossier aus Zürich und Ausgburg</t>
+  </si>
+  <si>
+    <t>Zürich und Augsburg</t>
+  </si>
+  <si>
+    <t>Testdatensatz Vacat</t>
+  </si>
+  <si>
+    <t>Aus Excel erzeugte Hierachie</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Datensatz in Test gelöscht</t>
+  </si>
+  <si>
+    <t>Testdatensatz gesperrt und PDF</t>
+  </si>
+  <si>
+    <t>gesperrtes_pdf.pdf</t>
+  </si>
+  <si>
+    <t>Testdatensatz privat mit PDF</t>
+  </si>
+  <si>
+    <t>privates_pdf.pdf</t>
+  </si>
+  <si>
+    <t>Testdatensatz Akteur am Namen erkennen</t>
+  </si>
+  <si>
+    <t>Test Ortsname Stadt als Stadt erkennen</t>
+  </si>
+  <si>
+    <t>Aargau</t>
+  </si>
+  <si>
+    <t>Test Name als Name erkennen</t>
+  </si>
+  <si>
+    <t>Witikon</t>
+  </si>
+  <si>
+    <t>Kränzle, Andreas (Historiker)</t>
+  </si>
+  <si>
+    <t>Gesperrtes Bild</t>
+  </si>
+  <si>
+    <t>Gesperrtes_Bild.png</t>
+  </si>
+  <si>
+    <t>Test 3</t>
   </si>
   <si>
     <t xml:space="preserve">Datensatz nach Import gesperrt, weil Bestands gesperrt </t>
   </si>
   <si>
-    <t xml:space="preserve">1992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test 1/pages</t>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>Test 1/pages</t>
   </si>
   <si>
     <t xml:space="preserve">Testdatensatz Pages </t>
   </si>
   <si>
-    <t xml:space="preserve">1500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1600</t>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>1600</t>
+  </si>
+  <si>
+    <t>Testdatensatz mit privatem pDF</t>
+  </si>
+  <si>
+    <t>provates_pdf2.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -884,12 +874,18 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -901,7 +897,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -909,65 +905,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1026,47 +980,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1074,12 +1044,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1108,7 +1078,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1129,7 +1099,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1180,7 +1150,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1198,71 +1168,73 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BK35"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:BK36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="22.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="10.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="14.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="33.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="4.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="7.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="28" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="22.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="28.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="31.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="30.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="29.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="18.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="30.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="38.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="1" width="27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="23.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="28.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="37.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="57" min="54" style="1" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="24.16"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="59" style="1" width="8.83"/>
+    <col min="1" max="1" width="11.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" customWidth="1"/>
+    <col min="6" max="6" width="4" style="1" customWidth="1"/>
+    <col min="7" max="9" width="15.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.83203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" style="1" customWidth="1"/>
+    <col min="15" max="16" width="14" style="1" customWidth="1"/>
+    <col min="17" max="17" width="22.1640625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="19" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="7" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.83203125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="33.1640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="4.5" style="1" customWidth="1"/>
+    <col min="24" max="24" width="21" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.83203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9" style="1" customWidth="1"/>
+    <col min="27" max="27" width="8" style="1" customWidth="1"/>
+    <col min="28" max="34" width="14" style="1" customWidth="1"/>
+    <col min="35" max="35" width="23.5" style="1" customWidth="1"/>
+    <col min="36" max="36" width="22.33203125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="18.6640625" style="1" customWidth="1"/>
+    <col min="38" max="38" width="28.1640625" style="1" customWidth="1"/>
+    <col min="39" max="39" width="12.83203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="31.6640625" style="1" customWidth="1"/>
+    <col min="41" max="41" width="23.5" style="1" customWidth="1"/>
+    <col min="42" max="42" width="30.5" style="1" customWidth="1"/>
+    <col min="43" max="43" width="29.5" style="1" customWidth="1"/>
+    <col min="44" max="44" width="18.6640625" style="1" customWidth="1"/>
+    <col min="45" max="45" width="30.5" style="1" customWidth="1"/>
+    <col min="46" max="46" width="38.83203125" style="1" customWidth="1"/>
+    <col min="47" max="47" width="16.5" style="1" customWidth="1"/>
+    <col min="48" max="49" width="27" style="1" customWidth="1"/>
+    <col min="50" max="50" width="23.5" style="1" customWidth="1"/>
+    <col min="51" max="51" width="33" style="1" customWidth="1"/>
+    <col min="52" max="52" width="28.1640625" style="1" customWidth="1"/>
+    <col min="53" max="53" width="37.6640625" style="1" customWidth="1"/>
+    <col min="54" max="57" width="8.83203125" style="1"/>
+    <col min="58" max="58" width="24.1640625" style="1" customWidth="1"/>
+    <col min="59" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:63" ht="16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1425,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>63</v>
       </c>
@@ -1487,7 +1459,7 @@
       <c r="N2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="O2" s="1">
         <v>1</v>
       </c>
       <c r="Q2" s="1" t="s">
@@ -1499,7 +1471,7 @@
       <c r="S2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T2" s="1" t="n">
+      <c r="T2" s="1">
         <v>0</v>
       </c>
       <c r="V2" s="1" t="s">
@@ -1521,7 +1493,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>63</v>
       </c>
@@ -1546,13 +1518,13 @@
       <c r="N3" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O3" s="1" t="n">
+      <c r="O3" s="1">
         <v>1</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="T3" s="1" t="n">
+      <c r="T3" s="1">
         <v>0</v>
       </c>
       <c r="V3" s="1" t="s">
@@ -1574,8 +1546,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:63" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
         <v>6</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -1599,13 +1571,13 @@
       <c r="N4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="O4" s="1" t="n">
+      <c r="O4" s="1">
         <v>1</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="T4" s="1">
         <v>0</v>
       </c>
       <c r="V4" s="1" t="s">
@@ -1617,7 +1589,7 @@
       <c r="X4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Z4" s="1" t="n">
+      <c r="Z4" s="1">
         <v>2016</v>
       </c>
       <c r="AA4" s="1" t="s">
@@ -1639,7 +1611,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>102</v>
       </c>
@@ -1664,7 +1636,7 @@
       <c r="N5" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="O5" s="1" t="n">
+      <c r="O5" s="1">
         <v>1</v>
       </c>
       <c r="Q5" s="4" t="s">
@@ -1676,7 +1648,7 @@
       <c r="S5" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="T5" s="1">
         <v>0</v>
       </c>
       <c r="V5" s="1" t="s">
@@ -1698,7 +1670,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>102</v>
       </c>
@@ -1723,7 +1695,7 @@
       <c r="N6" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="O6" s="1">
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
@@ -1732,7 +1704,7 @@
       <c r="S6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="V6" s="1" t="s">
@@ -1748,7 +1720,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>119</v>
       </c>
@@ -1773,7 +1745,7 @@
       <c r="N7" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="O7" s="1" t="n">
+      <c r="O7" s="1">
         <v>1</v>
       </c>
       <c r="Q7" s="4" t="s">
@@ -1782,7 +1754,7 @@
       <c r="R7" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="T7" s="1" t="n">
+      <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="V7" s="1" t="s">
@@ -1798,7 +1770,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>119</v>
       </c>
@@ -1823,7 +1795,7 @@
       <c r="N8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="O8" s="1">
         <v>1</v>
       </c>
       <c r="Q8" s="4" t="s">
@@ -1832,7 +1804,7 @@
       <c r="S8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T8" s="1" t="n">
+      <c r="T8" s="1">
         <v>0</v>
       </c>
       <c r="V8" s="1" t="s">
@@ -1848,7 +1820,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>119</v>
       </c>
@@ -1873,7 +1845,7 @@
       <c r="N9" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="O9" s="1">
         <v>1</v>
       </c>
       <c r="Q9" s="4" t="s">
@@ -1882,7 +1854,7 @@
       <c r="S9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="T9" s="1">
         <v>0</v>
       </c>
       <c r="V9" s="1" t="s">
@@ -1898,7 +1870,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>119</v>
       </c>
@@ -1923,7 +1895,7 @@
       <c r="N10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="O10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="4" t="s">
@@ -1932,7 +1904,7 @@
       <c r="S10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T10" s="1" t="n">
+      <c r="T10" s="1">
         <v>0</v>
       </c>
       <c r="V10" s="1" t="s">
@@ -1948,7 +1920,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>140</v>
       </c>
@@ -1973,7 +1945,7 @@
       <c r="N11" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="O11" s="1" t="n">
+      <c r="O11" s="1">
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="s">
@@ -1982,7 +1954,7 @@
       <c r="S11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="T11" s="1">
         <v>0</v>
       </c>
       <c r="V11" s="1" t="s">
@@ -2001,7 +1973,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>149</v>
       </c>
@@ -2038,7 +2010,7 @@
       <c r="N12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="O12" s="1">
         <v>1</v>
       </c>
       <c r="Q12" s="1" t="s">
@@ -2050,7 +2022,7 @@
       <c r="S12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="T12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1" t="s">
@@ -2059,7 +2031,7 @@
       <c r="Y12" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Z12" s="1" t="n">
+      <c r="Z12" s="1">
         <v>2016</v>
       </c>
       <c r="AA12" s="1" t="s">
@@ -2144,7 +2116,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>149</v>
       </c>
@@ -2169,10 +2141,10 @@
       <c r="N13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="O13" s="1">
         <v>1</v>
       </c>
-      <c r="T13" s="1" t="n">
+      <c r="T13" s="1">
         <v>0</v>
       </c>
       <c r="V13" s="1" t="s">
@@ -2185,7 +2157,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>149</v>
       </c>
@@ -2210,10 +2182,10 @@
       <c r="N14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="O14" s="1">
         <v>2</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="T14" s="1">
         <v>0</v>
       </c>
       <c r="V14" s="5" t="s">
@@ -2226,7 +2198,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -2251,10 +2223,10 @@
       <c r="N15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="O15" s="1">
         <v>1</v>
       </c>
-      <c r="T15" s="1" t="n">
+      <c r="T15" s="1">
         <v>0</v>
       </c>
       <c r="AE15" s="1" t="s">
@@ -2264,7 +2236,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>149</v>
       </c>
@@ -2289,10 +2261,10 @@
       <c r="N16" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="O16" s="1">
         <v>1</v>
       </c>
-      <c r="T16" s="1" t="n">
+      <c r="T16" s="1">
         <v>0</v>
       </c>
       <c r="V16" s="1" t="s">
@@ -2301,11 +2273,11 @@
       <c r="AE16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AH16" s="1" t="n">
+      <c r="AH16" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>149</v>
       </c>
@@ -2333,17 +2305,17 @@
       <c r="N17" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="O17" s="1">
         <v>1</v>
       </c>
-      <c r="T17" s="1" t="n">
+      <c r="T17" s="1">
         <v>0</v>
       </c>
       <c r="AE17" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>149</v>
       </c>
@@ -2368,13 +2340,13 @@
       <c r="N18" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O18" s="1" t="n">
+      <c r="O18" s="1">
         <v>1</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="T18" s="1" t="n">
+      <c r="T18" s="1">
         <v>0</v>
       </c>
       <c r="V18" s="1" t="s">
@@ -2384,7 +2356,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>149</v>
       </c>
@@ -2409,10 +2381,10 @@
       <c r="N19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="O19" s="1">
         <v>1</v>
       </c>
-      <c r="T19" s="1" t="n">
+      <c r="T19" s="1">
         <v>0</v>
       </c>
       <c r="V19" s="1" t="s">
@@ -2422,7 +2394,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>149</v>
       </c>
@@ -2447,10 +2419,10 @@
       <c r="N20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="O20" s="1">
         <v>1</v>
       </c>
-      <c r="T20" s="1" t="n">
+      <c r="T20" s="1">
         <v>0</v>
       </c>
       <c r="AE20" s="1" t="s">
@@ -2463,7 +2435,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>208</v>
       </c>
@@ -2476,14 +2448,14 @@
       <c r="N21" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="O21" s="1">
         <v>1</v>
       </c>
-      <c r="T21" s="1" t="n">
+      <c r="T21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>208</v>
       </c>
@@ -2505,7 +2477,7 @@
       <c r="N22" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="O22" s="1" t="n">
+      <c r="O22" s="1">
         <v>1</v>
       </c>
       <c r="P22" s="1" t="s">
@@ -2517,7 +2489,7 @@
       <c r="R22" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="T22" s="1" t="n">
+      <c r="T22" s="1">
         <v>0</v>
       </c>
       <c r="AF22" s="1" t="s">
@@ -2542,7 +2514,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>222</v>
       </c>
@@ -2567,14 +2539,14 @@
       <c r="N23" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="O23" s="1">
         <v>1</v>
       </c>
       <c r="Q23" s="1" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>222</v>
       </c>
@@ -2599,14 +2571,14 @@
       <c r="N24" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="O24" s="1">
         <v>1</v>
       </c>
       <c r="AC24" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>149</v>
       </c>
@@ -2635,7 +2607,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>228</v>
       </c>
@@ -2658,7 +2630,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>228</v>
       </c>
@@ -2669,7 +2641,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
@@ -2704,7 +2676,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>149</v>
       </c>
@@ -2742,7 +2714,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>149</v>
       </c>
@@ -2768,7 +2740,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>149</v>
       </c>
@@ -2788,7 +2760,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>149</v>
       </c>
@@ -2811,7 +2783,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>149</v>
       </c>
@@ -2831,7 +2803,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>248</v>
       </c>
@@ -2854,7 +2826,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" spans="1:45" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>149</v>
       </c>
@@ -2904,13 +2876,71 @@
         <v>78</v>
       </c>
     </row>
+    <row r="36" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="A36" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E36" s="6">
+        <v>2000</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6">
+        <v>2000</v>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="O36" s="6">
+        <v>1</v>
+      </c>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6"/>
+      <c r="AI36" s="6"/>
+      <c r="AJ36" s="6"/>
+      <c r="AK36" s="6"/>
+      <c r="AL36" s="6"/>
+      <c r="AM36" s="6"/>
+      <c r="AN36" s="6"/>
+      <c r="AO36" s="6"/>
+      <c r="AP36" s="6"/>
+      <c r="AQ36" s="6"/>
+      <c r="AR36" s="6"/>
+      <c r="AS36" s="6"/>
+    </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/anton_new_import_test_data.xlsx
+++ b/anton_new_import_test_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ak/Dropbox/anton_import_test_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81FCEAA-40B4-0A4F-8835-80DE9581B8C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F3CD74-9655-024D-95ED-F419BA566266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="27900" windowHeight="17380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -299,7 +299,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
-        <charset val="1"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">This work has been released into the </t>
     </r>
@@ -845,14 +845,14 @@
     <t>Testdatensatz mit privatem pDF</t>
   </si>
   <si>
-    <t>provates_pdf2.pdf</t>
+    <t>pdf-media_private.pdf</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -884,6 +884,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
